--- a/Hemapreetha_Timesheet_1July-31July.xlsx
+++ b/Hemapreetha_Timesheet_1July-31July.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gunas\Hema\git-my\vinove\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11F07B9-D830-465D-B523-203AC3A01C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B8BDC0-567E-4EF5-B8FE-4EF1966DBEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
   <si>
     <t>Monthly Timesheet</t>
   </si>
@@ -146,9 +146,6 @@
 Support 512478: [PRIIPs EU] - [ARES] issue 4 pages in French</t>
   </si>
   <si>
-    <t>Limited to 170 hours</t>
-  </si>
-  <si>
     <t>07-31-2025</t>
   </si>
   <si>
@@ -220,6 +217,15 @@
 ============
 Product Backlog Item 507534: Plus Documents PT-3621 Bantleon Invest GmbH - ESG Changes
 Product Backlog Item 462523: PT-2701 - Valiant Bank - ESG Report Design Updates</t>
+  </si>
+  <si>
+    <t>FEFundInfo
+============
+Product Backlog Item 504531: PT-2409 - ZIL Factsheet Migration +Docs - Theme amendments
+Product Backlog Item 515890: Change Request - Indigo Digital Factsheet PDF Module</t>
+  </si>
+  <si>
+    <t>Limited to 195.5 hours</t>
   </si>
 </sst>
 </file>
@@ -483,6 +489,15 @@
     <xf numFmtId="15" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
@@ -491,9 +506,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -504,12 +516,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -860,25 +866,25 @@
   <sheetData>
     <row r="1" spans="2:9" ht="17.25" thickBot="1"/>
     <row r="2" spans="2:9" ht="59.1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="25"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="4" spans="2:9" ht="30" customHeight="1">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
       <c r="G4" s="3" t="s">
         <v>2</v>
       </c>
@@ -890,16 +896,16 @@
       <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
       <c r="G5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="30" customHeight="1">
@@ -909,13 +915,13 @@
       <c r="C7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="30"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="32"/>
       <c r="I7" s="7" t="s">
         <v>8</v>
       </c>
@@ -1136,7 +1142,7 @@
         <v>8.5</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18"/>
       <c r="F21" s="18"/>
@@ -1168,7 +1174,7 @@
         <v>8.5</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E23" s="18"/>
       <c r="F23" s="18"/>
@@ -1184,7 +1190,7 @@
         <v>8.5</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E24" s="18"/>
       <c r="F24" s="18"/>
@@ -1200,7 +1206,7 @@
         <v>8.5</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E25" s="18"/>
       <c r="F25" s="18"/>
@@ -1208,15 +1214,15 @@
       <c r="H25" s="19"/>
       <c r="I25" s="14"/>
     </row>
-    <row r="26" spans="2:9" ht="57.75" customHeight="1">
+    <row r="26" spans="2:9" ht="16.5" customHeight="1">
       <c r="B26" s="7">
         <v>45857</v>
       </c>
       <c r="C26" s="8">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="E26" s="18"/>
       <c r="F26" s="18"/>
@@ -1224,15 +1230,15 @@
       <c r="H26" s="19"/>
       <c r="I26" s="14"/>
     </row>
-    <row r="27" spans="2:9" ht="73.5" customHeight="1">
+    <row r="27" spans="2:9" ht="16.5" customHeight="1">
       <c r="B27" s="7">
         <v>45858</v>
       </c>
       <c r="C27" s="8">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E27" s="18"/>
       <c r="F27" s="18"/>
@@ -1240,15 +1246,15 @@
       <c r="H27" s="19"/>
       <c r="I27" s="14"/>
     </row>
-    <row r="28" spans="2:9" ht="21.75" customHeight="1">
+    <row r="28" spans="2:9" ht="60.75" customHeight="1">
       <c r="B28" s="7">
         <v>45859</v>
       </c>
       <c r="C28" s="8">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
@@ -1256,15 +1262,15 @@
       <c r="H28" s="19"/>
       <c r="I28" s="14"/>
     </row>
-    <row r="29" spans="2:9" ht="21.75" customHeight="1">
+    <row r="29" spans="2:9" ht="78" customHeight="1">
       <c r="B29" s="7">
         <v>45860</v>
       </c>
       <c r="C29" s="8">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="E29" s="18"/>
       <c r="F29" s="18"/>
@@ -1280,7 +1286,7 @@
         <v>8.5</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E30" s="18"/>
       <c r="F30" s="18"/>
@@ -1296,7 +1302,7 @@
         <v>8.5</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E31" s="18"/>
       <c r="F31" s="18"/>
@@ -1312,7 +1318,7 @@
         <v>8.5</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E32" s="18"/>
       <c r="F32" s="18"/>
@@ -1360,7 +1366,7 @@
         <v>8.5</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E35" s="18"/>
       <c r="F35" s="18"/>
@@ -1376,7 +1382,7 @@
         <v>8.5</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E36" s="18"/>
       <c r="F36" s="18"/>
@@ -1392,7 +1398,7 @@
         <v>8.5</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E37" s="18"/>
       <c r="F37" s="18"/>
@@ -1404,8 +1410,12 @@
       <c r="B38" s="7">
         <v>45869</v>
       </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>40</v>
+      </c>
       <c r="E38" s="18"/>
       <c r="F38" s="18"/>
       <c r="G38" s="18"/>
@@ -1418,42 +1428,42 @@
       </c>
       <c r="C39" s="10">
         <f>SUM(C8:C38)</f>
-        <v>187</v>
-      </c>
-      <c r="D39" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="E39" s="32"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="32"/>
+        <v>195.5</v>
+      </c>
+      <c r="D39" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
     </row>
     <row r="41" spans="2:9" ht="30" customHeight="1">
-      <c r="B41" s="31" t="s">
+      <c r="B41" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C41" s="31"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
       <c r="G41" s="16" t="s">
         <v>11</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="2:9">
       <c r="B42" s="12"/>
     </row>
     <row r="43" spans="2:9" ht="30" customHeight="1">
-      <c r="B43" s="31" t="s">
+      <c r="B43" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C43" s="31"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="26"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
       <c r="G43" s="16" t="s">
         <v>11</v>
       </c>
@@ -1463,13 +1473,13 @@
       <c r="B44" s="12"/>
     </row>
     <row r="45" spans="2:9" ht="30" customHeight="1">
-      <c r="B45" s="31" t="s">
+      <c r="B45" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C45" s="31"/>
-      <c r="D45" s="26"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="26"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
       <c r="G45" s="16" t="s">
         <v>11</v>
       </c>
@@ -1477,6 +1487,32 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D34:H34"/>
     <mergeCell ref="D35:H35"/>
     <mergeCell ref="D36:H36"/>
     <mergeCell ref="D37:H37"/>
@@ -1493,32 +1529,6 @@
     <mergeCell ref="D12:H12"/>
     <mergeCell ref="D13:H13"/>
     <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D34:H34"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -1532,9 +1542,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1652,19 +1665,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2557F9BC-8CE0-4467-BBA0-44089D18E7E7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DBB90D6-6CF2-454A-903E-412076510F41}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1686,9 +1695,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DBB90D6-6CF2-454A-903E-412076510F41}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2557F9BC-8CE0-4467-BBA0-44089D18E7E7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>